--- a/SCRAPING/wisataV2_updated_updated.xlsx
+++ b/SCRAPING/wisataV2_updated_updated.xlsx
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>126000</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4702,10 +4702,18 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>matic.malangkab.go.id</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://matic.malangkab.go.id/listing/desa-wisata-senggreng</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5684,7 +5692,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5729,10 +5737,18 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+        <v>5000</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>sidita.disbudpar.jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://sidita.disbudpar.jatimprov.go.id/destinasi/detail/7ee797c1c8f6ced07344e82e65dc270933b1e7e31d4d07e431e1af51479fb2cab7b5e24dd96fc4b1171cd06b27dccaf82c2531fb9071c636a39e602e1af325bc</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5991,16 +6007,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>tiket.com</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQWAfdEE5i1/</t>
+          <t>https://www.tiket.com/id-id/to-do/batu-night-spectacular</t>
         </is>
       </c>
     </row>
@@ -6351,16 +6367,16 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>reddoorz.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.reddoorz.com/id-id/blog/places-to-visit/jatim-park-3</t>
+          <t>https://www.instagram.com/reel/DOdNUjXkqdd/</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6502,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6495,7 +6511,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DXA52tlE8Ac/</t>
+          <t>https://www.instagram.com/p/DOH-qO6AS7-/</t>
         </is>
       </c>
     </row>
@@ -6936,16 +6952,16 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/museum-tubuh</t>
+          <t>https://www.instagram.com/museumtubuh/</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7721,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>traveloka.com</t>
+          <t>paketwisatabromo.co.id</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.traveloka.com/id-id/explore/destination/mengenal-bukit-jengkoang-inilah-fakta-dan-daya-tarik-wisatanya-acc/535945</t>
+          <t>https://www.paketwisatabromo.co.id/bukit-jengkoang/</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7987,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8016,7 +8032,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -8061,16 +8077,16 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>24travel.id</t>
+          <t>adamputratravel.com</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://24travel.id/brakseng-malang/</t>
+          <t>https://adamputratravel.com/wisata-alam-brakseng-batu/</t>
         </is>
       </c>
     </row>
@@ -8151,16 +8167,16 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>travelspromo.com</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CZsx6yhh2o9/</t>
+          <t>https://travelspromo.com/htm-wisata/pantai-ngantep-malang/</t>
         </is>
       </c>
     </row>
@@ -8693,8 +8709,16 @@
       <c r="I184" t="n">
         <v>0</v>
       </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>toyota.astra.co.id</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://www.toyota.astra.co.id/corporate-information/news-promo/read/jangan-sampai-salah-masuk-ini-arti-simbol-rest-area-di-jalan-tol-yang-wajib-dipahami</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9403,16 +9427,16 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>jtp.id</t>
+          <t>tiket.com</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://jtp.id/bns/batu-night-spectacular-primadona-wisata-malam-di-kota-malang-dan-batu/index.html</t>
+          <t>https://www.tiket.com/id-id/to-do/batu-night-spectacular</t>
         </is>
       </c>
     </row>
@@ -9493,16 +9517,16 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>wesb-nandhi.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>https://wesb-nandhi.com/</t>
+          <t>https://www.instagram.com/reel/DNkeLS6yzju/</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9562,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -9808,7 +9832,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9817,7 +9841,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/Cu6kYWHJdFo/?hl=id</t>
+          <t>https://www.instagram.com/jatimparkdua/</t>
         </is>
       </c>
     </row>
@@ -9943,16 +9967,16 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jatimparkdua/</t>
+          <t>https://www.traveloka.com/id-id/activities/indonesia/product/jatim-park-2-tickets-batu-secret-zoo-museum-satwa-2000625477100</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10192,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0</v>
+        <v>104500</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -10258,7 +10282,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -10348,16 +10372,16 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>traveloka.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>https://www.traveloka.com/id-id/explore/destination/pasar-apung-batu-tradisi-unik-di-indonesia-acc/496849</t>
+          <t>https://www.instagram.com/reel/DBVx2f8JD1L/?hl=id</t>
         </is>
       </c>
     </row>
@@ -10665,8 +10689,16 @@
       <c r="I228" t="n">
         <v>0</v>
       </c>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DFZuP1XR3qB/</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -11870,16 +11902,16 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>sidita.disbudpar.jatimprov.go.id</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>https://sidita.disbudpar.jatimprov.go.id/destinasi/detail/360fc66ea54c2c5028bfdfb64661bd665d625ede5eb33e9ea2fe5ac79e670a6aa78e845b60f511c444d2bbf1318fdb10ca78e357852c10b77fa6a3818367167d</t>
+          <t>https://www.instagram.com/reel/DL3w6-_SFpe/</t>
         </is>
       </c>
     </row>
@@ -12185,16 +12217,16 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>atourin.com</t>
+          <t>malangtimes.com</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>https://atourin.com/destination/malang/taman-jurang-toleh</t>
+          <t>https://www.malangtimes.com/baca/161254/20171105/063226/wisata-jurang-toleh-di-sumberpucung-suguhkan-danau-dan-taman-bunga</t>
         </is>
       </c>
     </row>
@@ -12320,16 +12352,16 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>matic.malangkab.go.id</t>
+          <t>malymarszalek.edu.pl</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>https://matic.malangkab.go.id/listing/monumen-peniwen-affair</t>
+          <t>https://malymarszalek.edu.pl/kromengan-malang/</t>
         </is>
       </c>
     </row>
@@ -12770,16 +12802,16 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>waze.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>https://www.waze.com/id/live-map/directions/id/jawa-timur/toko-benang-rajut-julia-house?to=place.ChIJ6SM0niUo1i0RQPl1QGFpZ1A</t>
+          <t>https://www.instagram.com/reel/DFIDpOlyR7o/</t>
         </is>
       </c>
     </row>
@@ -12907,8 +12939,16 @@
       <c r="I278" t="n">
         <v>0</v>
       </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>kumparan.com</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>https://kumparan.com/jendela-dunia/taman-krida-budaya-malang-tarif-masuk-dan-fasilitas-yang-tersedia-22ljsIWIqAs</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -13302,16 +13342,16 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>binus.ac.id</t>
+          <t>mcc.malangkota.go.id</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>https://binus.ac.id/malang/dkv/2023/06/05/semeru-art-gallery-malang-an-overview-by-jennifer/</t>
+          <t>https://mcc.malangkota.go.id/event/ruangan/creative-city-planing-galery-45</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13387,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -13356,7 +13396,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C27LxGWLJiu/</t>
+          <t>https://www.instagram.com/reel/CwwVondrJCh/</t>
         </is>
       </c>
     </row>
@@ -14157,16 +14197,16 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>sidita.disbudpar.jatimprov.go.id</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>https://sidita.disbudpar.jatimprov.go.id/destinasi/detail/a8beb30b9c8e3b868e66bbe97b9f615567b69dda10fee72ceea1e4ca4523259080974a4bbfa0cb95f42ace13b4ab85c53897546807c8653ee1586059e62f4c3c-2</t>
+          <t>https://id.trip.com/travel-guide/attraction/gondanglegi/kali-mbureng-136821322/</t>
         </is>
       </c>
     </row>
@@ -14654,8 +14694,16 @@
       <c r="I317" t="n">
         <v>0</v>
       </c>
-      <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>id.trip.com</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>https://id.trip.com/travel-guide/attraction/malang-city/taman-cerme-gramophone-142473607/</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -14914,16 +14962,16 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>malangkota.go.id</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>https://malangkota.go.id/2017/12/24/diresmikan-taman-dempo-jadi-kado-akhir-tahun/</t>
+          <t>https://id.trip.com/travel-guide/attraction/malang-city/taman-dempo-136945992/</t>
         </is>
       </c>
     </row>
@@ -15499,7 +15547,7 @@
         </is>
       </c>
       <c r="I336" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -15508,7 +15556,7 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DXAz5uuvnqV/</t>
+          <t>https://www.instagram.com/reel/DWQajAkido7/</t>
         </is>
       </c>
     </row>
@@ -15593,12 +15641,12 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>lemon8-app.com</t>
+          <t>resimojo.mojokertokab.go.id</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>https://www.lemon8-app.com/@resha.rizky/7582794170150945298?region=id</t>
+          <t>https://resimojo.mojokertokab.go.id/Riset/1732091258_1.%20DRAFT%20LAPORAN%20AKHIR%20rev%203.pdf</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15727,7 @@
         </is>
       </c>
       <c r="I340" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -15949,7 +15997,7 @@
         </is>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -15958,7 +16006,7 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jatimparkdua/</t>
+          <t>https://www.instagram.com/reel/Cu6kYWHJdFo/?hl=id</t>
         </is>
       </c>
     </row>
@@ -15994,16 +16042,16 @@
         </is>
       </c>
       <c r="I347" t="n">
-        <v>0</v>
+        <v>39600</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>jtp.id</t>
+          <t>tiket.com</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>https://jtp.id/jatimpark1/get-to-know-more-jawa-timur-park-1/index.html</t>
+          <t>https://www.tiket.com/id-id/to-do/jatim-park-1</t>
         </is>
       </c>
     </row>
@@ -16221,8 +16269,16 @@
       <c r="I352" t="n">
         <v>0</v>
       </c>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>id.trip.com</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>https://id.trip.com/travel-guide/attraction/karang-ploso/wisata-religi-gunung-mujur-146740307/</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -16661,16 +16717,16 @@
         </is>
       </c>
       <c r="I362" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CUOvwjVPKUh/</t>
+          <t>https://id.trip.com/travel-guide/attraction/gedangan/pantai-gopit-136982688/</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17122,7 @@
         </is>
       </c>
       <c r="I371" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -17200,10 +17256,12 @@
           <t>https://www.google.com/maps/place/Oude+Indi%C3%AB+Aquaduct+bij+Boeloelawang+-+Malang+Regentschap+-+Wisata+Talang/data=!4m7!3m6!1s0x2dd621412f0eccbd:0x3efbe1b8392383ce!8m2!3d-8.0870516!4d112.6463769!16s%2Fg%2F11hyg4gxm2!19sChIJvcwOL0Eh1i0RzoMjObjh-z4?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I374" t="n">
-        <v>0</v>
-      </c>
-      <c r="J374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
@@ -17237,10 +17295,12 @@
           <t>https://www.google.com/maps/place/Siphon+Metro+Talangagung+Kepanjen/data=!4m7!3m6!1s0x2e789f482162fdb5:0xc7996e38d99c2ab0!8m2!3d-8.1288081!4d112.5599863!16s%2Fg%2F11j5g8bpt6!19sChIJtf1iIUifeC4RsCqc2Thumcc?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I375" t="n">
-        <v>0</v>
-      </c>
-      <c r="J375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -17680,18 +17740,10 @@
         </is>
       </c>
       <c r="I385" t="n">
-        <v>70000</v>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>tirtajayatravel.com</t>
-        </is>
-      </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>https://tirtajayatravel.com/museum-angkut-malang-tiket-masuk-dan-rute/</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -17725,16 +17777,16 @@
         </is>
       </c>
       <c r="I386" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>beritasatu.com</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DBaaoW0y2w1/</t>
+          <t>https://www.beritasatu.com/news/478491/unik-tpu-di-malang-ini-dijadikan-destinasi-wisata</t>
         </is>
       </c>
     </row>
@@ -20655,7 +20707,7 @@
         </is>
       </c>
       <c r="I452" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="J452" t="inlineStr">
         <is>
@@ -21059,9 +21111,19 @@
           <t>https://www.google.com/maps/place/OG+Durian/data=!4m7!3m6!1s0x2dd621f90e1eb803:0x2676277a2feca1ab!8m2!3d-8.1306309!4d112.663318!16s%2Fg%2F11y28pd1m5!19sChIJA7geDvkh1i0Rq6HsL3ondiY?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
-      <c r="K461" t="inlineStr"/>
+      <c r="I461" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/duriangarden.id/</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -21635,7 +21697,7 @@
         </is>
       </c>
       <c r="I474" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J474" t="inlineStr">
         <is>
@@ -21724,9 +21786,19 @@
           <t>https://www.google.com/maps/place/Patung+Singo+Edan+Arema/data=!4m7!3m6!1s0x2dd6283c114bacbf:0xd0aefdd0b4975b22!8m2!3d-7.977314!4d112.6366485!16s%2Fg%2F11cjhc28p6!19sChIJv6xLETwo1i0RIluXtND9rtA?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>kelkiduldalem.malangkota.go.id</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>https://kelkiduldalem.malangkota.go.id/2016/08/08/5-singa-ter-edan-di-kandang-singa/</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -22299,9 +22371,19 @@
           <t>https://www.google.com/maps/place/Taman+Indragiri+Malang/data=!4m7!3m6!1s0x2dd62929a77d982f:0x9f7967fe98455e65!8m2!3d-7.9580063!4d112.6418657!16s%2Fg%2F11jv1gnwr0!19sChIJL5h9pykp1i0RZV5FmP5neZ8?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I489" t="inlineStr"/>
-      <c r="J489" t="inlineStr"/>
-      <c r="K489" t="inlineStr"/>
+      <c r="I489" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>malangtimes.com</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>https://malangtimes.com/baca/197291/20190717/110400/selesai-penataan-fasilitas-hutan-kota-indragiri-bakal-manjakan-para-lansia</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -22470,7 +22552,11 @@
         </is>
       </c>
       <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
@@ -22504,9 +22590,19 @@
           <t>https://www.google.com/maps/place/Kebun+Murbei/data=!4m7!3m6!1s0x2dd629b2b3433015:0x424742adf4ac410d!8m2!3d-7.9306506!4d112.6608826!16s%2Fg%2F11qfxh8vdz!19sChIJFTBDs7Ip1i0RDUGs9K1CR0I?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
-      <c r="K494" t="inlineStr"/>
+      <c r="I494" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DDTbsLDypCs/</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -22674,9 +22770,19 @@
           <t>https://www.google.com/maps/place/SANGGAR+SEMAR/data=!4m7!3m6!1s0x2dd6293b9f78576f:0x8d83d3ce8708872d!8m2!3d-7.9276929!4d112.6554293!16s%2Fg%2F11vbttyqdk!19sChIJb1d4nzsp1i0RLYcIh87Tg40?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
-      <c r="J498" t="inlineStr"/>
-      <c r="K498" t="inlineStr"/>
+      <c r="I498" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>id.trip.com</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>https://id.trip.com/travel-guide/attraction/blimbing/sanggar-semar-146669706/</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -22844,9 +22950,19 @@
           <t>https://www.google.com/maps/place/Wisata+Sumbersuko,+Randuagung/data=!4m7!3m6!1s0x2dd62b22c9e30eaf:0x5b540d1d64a25ba1!8m2!3d-7.8562826!4d112.6782911!16s%2Fg%2F11d_d1jsf3!19sChIJrw7jySIr1i0RoVuiZB0NVFs?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
-      <c r="K502" t="inlineStr"/>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>id.trip.com</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>https://id.trip.com/travel-guide/attraction/singosari/wisata-sumbersuko-randuagung-137092164/</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -23104,9 +23220,19 @@
           <t>https://www.google.com/maps/place/Rest+Area+84B+Malang+Strudel+Playland/data=!4m7!3m6!1s0x2dd62b001742429d:0x84beee5003f64a4e!8m2!3d-7.897184!4d112.6965623!16s%2Fg%2F11yz7q2hyh!19sChIJnUJCFwAr1i0RTkr2A1DuvoQ?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
-      <c r="J508" t="inlineStr"/>
-      <c r="K508" t="inlineStr"/>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DU2zZ_Tj9Z4/</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -23185,7 +23311,11 @@
         </is>
       </c>
       <c r="I510" t="inlineStr"/>
-      <c r="J510" t="inlineStr"/>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K510" t="inlineStr"/>
     </row>
     <row r="511">
